--- a/sample.xlsx
+++ b/sample.xlsx
@@ -558,174 +558,184 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">序号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">楼层</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">房间</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">开</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">关</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">制冷</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">制热</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通风</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">除湿</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">低速</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中速</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高速</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">自动</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">温度</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">室温</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风速值</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2F</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主卧</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">401</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">402</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">403</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">405</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">406</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">407</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">408</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">409</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">410</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">401</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">450</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:dimension ref="A1:Q2"/>
+  <ns0:sheetFormatPr defaultRowHeight="15"/>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">序号</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">楼层</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">房间</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">开</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">关</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">制冷</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">制热</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">通风</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">除湿</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">低速</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">中速</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">高速</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">自动</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">温度</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">室温</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="P1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">风速值</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>名称</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">2F</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">主卧</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">400</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">401</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">402</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">403</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">405</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">406</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">407</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="K2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">408</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="L2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">409</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="M2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">410</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="N2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">400</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="O2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">401</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="P2" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">450</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="Q2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>空调</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+</ns0:worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -16,28 +16,86 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24476A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5EEF6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26734D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFD6DEE6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD6DEE6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD6DEE6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD6DEE6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -47,695 +105,1322 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="106" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">项目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crestron xlsx_to_yaml.py 示例工作簿（仅含虚构数据）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">提示</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">复制本文件后填写真实楼层、房间、名称和 join 编号</t>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">设备接口与 HA 自动化填写指南</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">适用人员：HA 配置人员、快思聪编程人员、现场调试人员。
+本表是双方共用的接口对照表，也是 HA 配置生成的输入文件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">用途与分工</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">双方共同确认位置、名称和 join 编号；快思聪人员按表实现控制与实际状态反馈；HA 人员导入设备后填写关联实体 ID，生成自动化。修改接口前应同步给对方。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">先替换示例</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">所有设备、join 和 example_ 实体 ID 都是虚构示例，不可直接用于现场。复制本文件后替换真实数据；不需要的关联清空，保留表头。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一、工作簿怎么填</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">设备工作表：灯光、插座、窗帘、空调；一行是一台设备。说明页可自行补充，不参与转换。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">表头与格式</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">设备页第一行必须是表头，名称须精确一致；不要合并单元格、插入标题行或用公式生成接口值。列顺序可以调整。文件须保存为 .xlsx。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">楼层／房间／名称</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">三列均必填，如 1F／客厅／灯带。HA 按楼层和房间创建或复用位置，设备名取“名称”。快思聪端可按相同位置和名称对照接口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">名称重复</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">同一楼层房间内设备重名，HA 从 1 编号，如吊灯1、吊灯2；不同楼层的同名房间在 HA 中编号。重复的楼层＋房间表示同一位置，不必在表中人为分房。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">序号与留空</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">序号仅便于阅读，不是 join。未使用的可选接口留空，不填 0 或“-”；设备行的必填字段不能空。空行可忽略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">二、join 编号与运行值</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">蓝色表头中的接口列填“第几路信号”，不是设备当前值。数字量、模拟量分别编号，允许数字 400 与模拟 400 同时存在。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">数字量编号</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">范围 1–4096。列包括：开、关、停止、制冷、制热、通风、除湿、低速、中速、高速、自动。单元格只填十进制整数，如 400，不写 d400、1.0 或状态 0/1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">模拟量编号</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">范围 1–1024。列包括：亮度、色温、位置、温度、室温、风速值。填通道编号，如 201；不能把亮度 50%、色温 3000 或温度 26 当作编号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">重复编号</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">同类信号（数字/模拟）内，不同设备或不同含义应使用不同编号；只有明确共用同一信号时才复用，并由双方确认。转换器会提示重复编号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">三、快思聪对接约定</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">以下方向统一以 HA 为参照。请实现真实设备反馈，不要只把 HA 发出的命令原样返回。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">连接方式</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HA 监听 TCP，默认端口 10200（以现场 crestron.yaml 为准）；快思聪 TCP/IP Client 主动连接 HA，接好 XSIG 收发并启用断线重连。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="63" customHeight="1">
+      <c r="A16" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">控制／反馈方向</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HA → 快思聪：控制命令，进入快思聪接收/执行逻辑。
+快思聪 → HA：设备实际状态，进入 HA 显示/自动化逻辑。
+同一功能在收、发方向采用表中相同类型及编号；不要把两条方向接反。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">开关与停止命令</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">继电器灯、插座、空调的开/关，以及窗帘开/关/停止：HA 发送短脉冲（当前默认约 0.2 秒，高后回低）。快思聪执行后通过反馈方向返回状态；调光灯使用模拟亮度，不走这组成对开关列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">开关状态反馈</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">开机/打开时：对应“开”反馈为 1、“关”为 0；关机/关闭时反之。反馈应保持实际状态，不是按钮脉冲；窗帘运动等过渡期可暂不明确。双高/双低不会被 HA 当作确定开关状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">空调模式／风速</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">模式、风速是互斥保持电平：所选档位为 1，同组其他档位为 0，不是短脉冲。主控执行后回传实际档位；电源开关不应强制改变原模式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">反馈更新</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">HA 依靠主控推送，不轮询设备。现场面板改变开关、档位、温度或亮度时，主控须主动上报对应通道；连接或重连后应补报当前状态。界面预显示不等于设备已执行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">四、各类设备填法</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">以下“运行值”是设备通信时的数值含义；在设备表里仍只填 join 编号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="63" customHeight="1">
+      <c r="A22" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">灯光：调光／色温</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">调光灯填“亮度”；支持调色温再填“色温”，开/关列留空。
+运行值：亮度 0–65535（0 关，65535 全亮，50% 约 32768）；色温 2700–6500 K，按 K 原值传输。普通开灯恢复已记住的非零亮度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">灯光：继电器</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">只开关灯完整填写“开”“关”，亮度、色温留空；不能混填两种控制方式。“功能”列仅为说明，如 Relay、单色温、双色温，不代替实际 join 配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">插座</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">填写完整“开”“关”数字 join，在 HA 生成为插座类型 switch。可通过后面的绿色关联列绑定控制开关或人在传感器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">窗帘</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">填写“开”“关”“停止”；可选填“类型”“位置”。类型示例：curtain 布帘、shade 卷帘、awning 遮阳篷。位置运行值 0 全关、100 全开，HA 可下发目标位置，主控回传实际位置。暂不支持本模板的开关/人在关联。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">空调</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">必填“开”“关”；按支持能力填模式/风速数字 join、温度/室温模拟 join。温度是设定温度（双向），室温是测量温度（主控 → HA）。本集成按摄氏度整数原值处理，不乘 10；HA 设温范围 16–30°C。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">空调风速值</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">“风速值”列为历史接口保留，当前 HA 转换器不使用，不据此提供风速控制。当前使用低速/中速/高速/自动四根数字 join；这四列不填，就没有风速调节能力。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">五、HA 自动化关联</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">绿色表头只供 HA 自动化使用，与快思聪 join 分开。设备导入后，从 HA 复制现有的实体 ID；品牌不限，不填写 device_id、设备显示名称或 join 数字。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">HA关联开关实体ID</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">填写可远程开关并反馈状态的 switch.xxx；支持灯光、插座、空调。不要把被控插座自身又填作控制开关。空调关联只控制电源，不修改模式、温度或风速。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">HA关联人在实体ID</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">填写报告 on/off 的 binary_sensor.xxx（有人为 on、无人为 off）；只支持灯光、插座。空调暂不支持人在关联，不要自行填入该列；窗帘也不支持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="97" customHeight="1">
+      <c r="A31" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">一个单元格多个 ID</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">每行一个实体 ID，在单元格内换行（例如 Alt+Enter），不能用逗号连接。
+示例：
+switch.example_living_panel
+switch.example_living_remote
+支持同一设备关联多个开关、多个传感器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">一个控制源多台设备</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">将同一个 ID 填在多条设备行即可。样表“客厅灯带”和“客厅落地灯插座”共用 switch.example_living_panel 和 binary_sensor.example_living_presence。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">联动行为</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">开关与设备双向同步：任意设备开启算组开，全部明确关闭才算组关；组内已有设备开启时，开关 ON 不再强制开其余设备。多传感器任意有人则开启，全部持续无人 30 秒才关闭；不提供手动保持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">留空与名称查找</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">留空表示不关联，设备本身仍可导入；所有关联清空后重新生成并覆盖自动化，会移除旧关联。可用 tools/list_ha_entities.py 查询实体 ID 和位置；实体改名后应更新本表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">六、使用与联调顺序</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">先确认物理接口和反馈，再生成 HA 设备；设备注册成功后才能生成关联自动化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">第 1 步：双方核对</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">填写真实设备位置、名称、join；快思聪按表完成控制和反馈。设备导入 HA 后，再逐台核对开关、亮度、位置、温度和模式，确认现场面板操作能反馈至 HA。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="80" customHeight="1">
+      <c r="A37" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">第 2 步：导入设备</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">在项目根目录运行：
+python3 tools/xlsx_to_yaml.py --check 设备表.xlsx
+用 deploy_devices.py 或 deploy_to_ha.sh 生成/上传 crestron.yaml，按部署提示检查并重启 HA，等待设备注册。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="80" customHeight="1">
+      <c r="A38" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">第 3 步：生成关联</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">替换示例 HA 实体 ID 后先检查：
+python3 tools/xlsx_to_automations.py 设备表.xlsx --check-xlsx
+再运行 deploy_automations.py 读取 Excel 和 HA 注册表，生成 automations_manual.yaml；核对关联报告，确认上传后检查并重载自动化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">检查的边界</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">--check-xlsx 只检查填写格式和模板，不保证实体 ID 存在。正式生成需读取目标 HA 注册表；示例 example_ ID 不存在时会报错，这是正常保护。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="46" customHeight="1">
+      <c r="A40" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">后续修改</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">修改 join：双方同步程序和设备配置，关键 join 改动还可能改变 HA 设备/实体身份。只修改关联列：重新执行自动化第二步即可。生成会覆盖成品文件，优先修改本表或模板。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="46" customHeight="1">
+      <c r="A41" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">交付前确认</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">逐台核对实际状态反馈，并测试双向开关及无人延时关闭；存在旧自动化时先核对是否重复控制。调试空调模式应遵守现场热源/冷源条件，不要试开不支持的模式。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="50" customWidth="1"/>
+    <col min="11" max="11" width="50" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">楼层</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">房间</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">名称</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">功能</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">亮度</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">色温</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">开</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">关</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">HA关联开关实体ID</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">HA关联人在实体ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1F</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">客厅</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">灯带</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">双色温</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">201</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">switch.example_living_panel
+switch.example_living_remote</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">binary_sensor.example_living_presence
+binary_sensor.example_living_door_presence</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1F</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">餐厅</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">吊灯</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">单色温</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="J3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">switch.example_dining_panel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1F</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">走廊</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">壁灯</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Relay</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K4"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">楼层</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">房间</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">名称</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">开</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">关</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="G1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">HA关联开关实体ID</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">HA关联人在实体ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1F</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">客厅</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">落地灯插座</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">147</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">148</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">switch.example_living_panel</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">binary_sensor.example_living_presence</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">楼层</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">房间</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">名称</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">类型</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">开</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">关</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">停止</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">位置</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2F</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">女儿房</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">卷帘</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">shade</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">700</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">701</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">702</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">480</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">2F</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">主卧</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">布帘</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">curtain</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">704</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">705</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">706</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">481</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1F</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">露台</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">遮阳篷</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">awning</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">708</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">709</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">710</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">482</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I4"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:dimension ref="A1:Q2"/>
-  <ns0:sheetFormatPr defaultRowHeight="15"/>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">序号</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">楼层</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">房间</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">开</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">关</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">制冷</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">制热</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">通风</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">除湿</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">低速</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">中速</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="L1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">高速</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">自动</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="N1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">温度</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="O1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">室温</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="P1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">风速值</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="Q1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>名称</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">2F</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">主卧</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">400</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">401</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">402</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">403</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">405</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">406</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">407</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="K2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">408</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="L2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">409</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="M2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">410</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="N2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">400</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="O2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">401</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="P2" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">450</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="Q2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>空调</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="24"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">序号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">楼层</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">房间</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">名称</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">开</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">关</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">制冷</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">制热</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">通风</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">除湿</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">低速</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">中速</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">高速</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">自动</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">温度</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">室温</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">风速值</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="4">
+        <is>
+          <t xml:space="preserve">HA关联开关实体ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2F</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">主卧</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">空调</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">400</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">401</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">402</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">403</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">405</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">406</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">407</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">408</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">409</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">410</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">400</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">401</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">450</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">switch.example_bedroom_ac_panel</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R2"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
 </file>
--- a/sample.xlsx
+++ b/sample.xlsx
@@ -310,7 +310,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="46" customHeight="1">
+    <row r="17" ht="80" customHeight="1">
       <c r="A17" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">开关与停止命令</t>
@@ -318,7 +318,7 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">继电器灯、插座、空调的开/关，以及窗帘开/关/停止：HA 发送短脉冲（当前默认约 0.2 秒，高后回低）。快思聪执行后通过反馈方向返回状态；调光灯使用模拟亮度，不走这组成对开关列。</t>
+          <t xml:space="preserve">只开关灯、插座、空调的开/关，以及窗帘开/关/停止：HA 发送短脉冲（约 0.2 秒，高后回低）。调光灯开灯统一用模拟亮度恢复记忆；配置完整开/关时，关灯优先用数字关 Join，状态仍通过数字 Join 反馈；未配置时用亮度置零关灯。</t>
         </is>
       </c>
     </row>
@@ -370,7 +370,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="63" customHeight="1">
+    <row r="22" ht="144" customHeight="1">
       <c r="A22" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">灯光：调光／色温</t>
@@ -378,12 +378,12 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">调光灯填“亮度”；支持调色温再填“色温”，开/关列留空。
-运行值：亮度 0–65535（0 关，65535 全亮，50% 约 32768）；色温 2700–6500 K，按 K 原值传输。普通开灯恢复已记住的非零亮度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
+          <t xml:space="preserve">调光灯填“亮度”；支持调色温再填“色温”。有数字开关接口时完整填写“开”“关”：开灯先将亮度置零，等待0.1秒，再恢复记忆亮度，不发送数字开灯；关灯发送数字关命令，开关状态由数字反馈判断。没有数字开关时关灯通过亮度置零，开关状态按亮度判断。
+两种灯均保存最近非零亮度，零反馈不覆盖记忆；无有效记忆时开灯默认 100%。运行值：亮度 0–65535（50% 约 32768）；色温 2700–6500 K。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="5">
         <is>
           <t xml:space="preserve">灯光：继电器</t>
@@ -391,7 +391,7 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">只开关灯完整填写“开”“关”，亮度、色温留空；不能混填两种控制方式。“功能”列仅为说明，如 Relay、单色温、双色温，不代替实际 join 配置。</t>
+          <t xml:space="preserve">只开关灯完整填写“开”“关”，亮度、色温留空；调光灯允许亮度、色温与完整开/关共存，开关必须成对。“功能”列仅为说明，如 Relay、单色温、双色温，不代替实际 join 配置。</t>
         </is>
       </c>
     </row>
